--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260726_204803.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260726_204803.xlsx
@@ -5642,7 +5642,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260726_204803.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260726_204803.xlsx
@@ -5642,7 +5642,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260726_204803.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260726_204803.xlsx
@@ -5642,7 +5642,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260726_204803.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260726_204803.xlsx
@@ -5642,7 +5642,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
